--- a/Data/Input/TransaccionesSAP_Copy.xlsx
+++ b/Data/Input/TransaccionesSAP_Copy.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aci-cns\Documents\UiPath\AMP06_00_InformeSeguimientoRepuestos\Data\Input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF252158-D943-4D1F-8229-28EB981564C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DF16B7A-DE55-40F5-A275-AB9F706CD4FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E7D37262-4DB0-4AD2-A290-68AC6299F871}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
   <si>
     <t>Transaction</t>
   </si>
@@ -34,16 +34,19 @@
     <t>Step3</t>
   </si>
   <si>
-    <t>ZMG002_01</t>
-  </si>
-  <si>
-    <t>variante</t>
-  </si>
-  <si>
     <t>ejecutar</t>
   </si>
   <si>
     <t>Step4</t>
+  </si>
+  <si>
+    <t>COHV</t>
+  </si>
+  <si>
+    <t>checks</t>
+  </si>
+  <si>
+    <t>disposicion</t>
   </si>
 </sst>
 </file>
@@ -908,18 +911,21 @@
         <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" t="s">
         <v>4</v>
       </c>
-      <c r="B2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2" t="s">
-        <v>6</v>
+      <c r="D2" t="s">
+        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/Data/Input/TransaccionesSAP_Copy.xlsx
+++ b/Data/Input/TransaccionesSAP_Copy.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aci-cns\Documents\UiPath\AMP06_00_InformeSeguimientoRepuestos\Data\Input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DF16B7A-DE55-40F5-A275-AB9F706CD4FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{511B9735-C692-444B-AEC7-3A1E6781154F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E7D37262-4DB0-4AD2-A290-68AC6299F871}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
   <si>
     <t>Transaction</t>
   </si>
@@ -34,19 +34,13 @@
     <t>Step3</t>
   </si>
   <si>
-    <t>ejecutar</t>
-  </si>
-  <si>
     <t>Step4</t>
   </si>
   <si>
-    <t>COHV</t>
+    <t>ZPP029_1</t>
   </si>
   <si>
-    <t>checks</t>
-  </si>
-  <si>
-    <t>disposicion</t>
+    <t>BOM</t>
   </si>
 </sst>
 </file>
@@ -536,9 +530,8 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Énfasis1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -911,21 +904,15 @@
         <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
-        <v>6</v>
+      <c r="A2" t="s">
+        <v>5</v>
       </c>
       <c r="B2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
